--- a/数据表/LevelUpReward.xlsx
+++ b/数据表/LevelUpReward.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>#</t>
   </si>
@@ -46,6 +46,9 @@
     <t>IconAssetName</t>
   </si>
   <si>
+    <t>Rarity</t>
+  </si>
+  <si>
     <t>Modifiers</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>RarityType</t>
+  </si>
+  <si>
     <t>StatModifier[]</t>
   </si>
   <si>
@@ -70,6 +76,9 @@
     <t>图标资源名</t>
   </si>
   <si>
+    <t>道具品质</t>
+  </si>
+  <si>
     <t>道具属性</t>
   </si>
   <si>
@@ -82,6 +91,9 @@
     <t>Almighty_Icon</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
     <t>[{"StatType":"Attack","Value":0.05,"IsPercent":true}]</t>
   </si>
   <si>
@@ -91,7 +103,61 @@
     <t>脑</t>
   </si>
   <si>
+    <t>[{"StatType":"Critical","Value":0.05,"IsPercent":true}]</t>
+  </si>
+  <si>
     <t>鼻子</t>
+  </si>
+  <si>
+    <t>[{"StatType":"AbsorbRange","Value":0.05,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>腿</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MovementSpeed","Value":0.05,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>眼睛</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":0.05,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Attack","Value":0.15,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Critical","Value":0.15,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"AbsorbRange","Value":0.15,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MovementSpeed","Value":0.15,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":0.15,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Attack","Value":0.3,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"Critical","Value":0.3,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"AbsorbRange","Value":0.3,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MovementSpeed","Value":0.3,"IsPercent":true}]</t>
+  </si>
+  <si>
+    <t>[{"StatType":"MaxHealth","Value":0.3,"IsPercent":true}]</t>
   </si>
 </sst>
 </file>
@@ -707,15 +773,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1031,142 +1103,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="10.3636363636364" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="16.4545454545455" customWidth="1"/>
-    <col min="6" max="6" width="61.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="18.1818181818182" style="2" customWidth="1"/>
+    <col min="7" max="7" width="61.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
         <v>101</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="1">
         <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="1">
         <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>17</v>
+      <c r="G8" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="1">
+        <v>105</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="1">
+        <v>106</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="3">
+        <v>107</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="1">
+        <v>108</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="1">
+        <v>109</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="1">
+        <v>110</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="1">
+        <v>111</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="1">
+        <v>112</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="3">
+        <v>113</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="1">
+        <v>114</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="1">
+        <v>115</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="1">
+        <v>116</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="1">
+        <v>117</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="1">
+        <v>118</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
